--- a/www/download/COUNTRY.TUR.rpA2.xlsx
+++ b/www/download/COUNTRY.TUR.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>Turquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.045627307212723</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.0789471581670156</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.146341531977318</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.255318926481855</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.398062215139079</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>0.592708488209772</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1.12520113062774</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1.5011408945586</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>1.48873766149879</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1.43231589474083</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1.34334577326075</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1.42411600761669</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.29760586993406</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>1.28747681169652</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>1.54662060710616</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20.586</t>
+          <t>4.43941851202304</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.195</t>
+          <t>3.89566233721573</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.204</t>
+          <t>3.65963785288109</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.779</t>
+          <t>3.67381065614052</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.048</t>
+          <t>3.2347335535235</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>3.9100073911563</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.524</t>
+          <t>4.28759445495139</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>21.354</t>
+          <t>5.10813554109399</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21.147</t>
+          <t>4.68478444750952</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>21.732</t>
+          <t>4.26817555291243</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>21.956</t>
+          <t>4.69694672387477</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>21.093</t>
+          <t>4.86414204409664</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>20.738</t>
+          <t>4.76392327957974</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>21.194</t>
+          <t>2.16919521353102</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>21.275</t>
+          <t>2.56565355102731</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10.192</t>
+          <t>3.38868266841154</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.493</t>
+          <t>2.92902020661703</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>10.497</t>
+          <t>2.79117266743105</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10.782</t>
+          <t>2.74200345603273</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10.736</t>
+          <t>2.57476675219091</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.362</t>
+          <t>3.14767990653802</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11.051</t>
+          <t>3.59207086135524</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11.47</t>
+          <t>4.35847533795854</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11.529</t>
+          <t>4.01199862421258</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>11.812</t>
+          <t>3.54257997801001</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12.473</t>
+          <t>3.66313545717944</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12.479</t>
+          <t>3.76397362072495</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>12.535</t>
+          <t>3.57794018759569</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>12.937</t>
+          <t>1.48798782809388</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>12.768</t>
+          <t>1.82052193212652</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>42695.615</t>
+          <t>1.51712469739496</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44294.708</t>
+          <t>1.28096669049658</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44759.107</t>
+          <t>1.15847671431047</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43374.73</t>
+          <t>1.09422830143341</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>43618.102</t>
+          <t>1.14840764080338</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42290.063</t>
+          <t>1.38532964519898</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>42188.186</t>
+          <t>1.69601698893546</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>41613.735</t>
+          <t>1.95690594568802</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>41088.621</t>
+          <t>1.73427642775963</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>41681.976</t>
+          <t>1.51031522520867</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>42517.307</t>
+          <t>1.5813875829616</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>41001.067</t>
+          <t>1.67046262604027</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>39622.583</t>
+          <t>1.5838654430598</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>40258.093</t>
+          <t>0.417769611405615</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>40019.218</t>
+          <t>0.613356071168546</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>21136.968</t>
+          <t>76564092881.7809</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>21928.844</t>
+          <t>79531697958.4364</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22158.416</t>
+          <t>84277044082.2234</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>21473.141</t>
+          <t>84061255904.2412</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>21239.635</t>
+          <t>86898315477.0862</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>22266.289</t>
+          <t>90543161068.6546</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21661.432</t>
+          <t>86501422912.517</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>22352.358</t>
+          <t>88895180267.0534</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>22401.434</t>
+          <t>95425407746.6453</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22654.767</t>
+          <t>100056014485.738</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>24154.349</t>
+          <t>104512503276.352</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>24257.62</t>
+          <t>105468202863.7</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23949.859</t>
+          <t>107327016969.66</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24573.739</t>
+          <t>113252336590.268</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>24016.797</t>
+          <t>98297919601.1226</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.62</t>
+          <t>10871821569.3246</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>12649292585.7376</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>13536784516.6845</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.36</t>
+          <t>13427768545.6196</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>13741413662.713</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.65</t>
+          <t>12809006627.7098</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24.72</t>
+          <t>11414018142.3802</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>25.84</t>
+          <t>10559418930.4441</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>11611224115.7988</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>12557425351.2796</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>12990998667.146</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>26.81</t>
+          <t>12780495812.217</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>27.42</t>
+          <t>13205655689.2183</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>24916308159.978</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>21936863473.7041</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>22.46</t>
+          <t>5586268.81669096</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>23.4</t>
+          <t>5515075.49432339</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>5524451.74827682</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>5469510.7178199</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>5862986.20933506</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>5710304.25080494</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25.41</t>
+          <t>7145941.01989042</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25.8</t>
+          <t>6673447.9438125</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>5398710.1727759</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26.77</t>
+          <t>4534173.47024936</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>3997229.31723308</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>27.76</t>
+          <t>3764990.75293201</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>3167421.58079506</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>2747891.787503</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>2975926.81689461</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>57.93</t>
+          <t>184475.414437707</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>56.09</t>
+          <t>194499.597681306</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>194794.341827437</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.19</t>
+          <t>186871.849327706</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52.87</t>
+          <t>192667.159142925</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>184567.523678258</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>49.87</t>
+          <t>179178.556189885</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>48.36</t>
+          <t>181242.160084095</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>195443.019489659</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>211811.131831484</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>236917.205880429</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>241927.974060132</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>264808.326630918</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>298480.15473054</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>271188.039038211</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>27.22</t>
+          <t>333984.006337955</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>345869.689597967</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>360464.433761617</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>355109.907311466</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>378746.30783657</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>396883.400163224</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>365765.750307113</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>380719.88913226</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>437565.017308534</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>497613.882766105</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>552868.773468126</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>580680.043028901</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>662436.274041161</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>763596.495707922</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>612597.623315582</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>2.64985828491068</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>2.33106979295476</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>2.19227558835332</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>2.16068456330658</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>2.09724449423553</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>2.55130042615116</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>2.98070105769992</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>3.55965467036929</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>3.30086312965534</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>2.89480131201017</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>3.11498496979896</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>3.2660539937754</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>3.20138383322121</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>1.31540422623517</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>1.66238768161214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>50285.1103942363</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>54077.1270264984</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>57121.9452990314</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>60402.6002907757</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>39.08</t>
+          <t>55702.0597379603</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>60834.3176809768</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>47348.8132081669</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>48630.5337446611</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.61</t>
+          <t>59459.8785830553</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>77499.3092627744</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>32.79</t>
+          <t>89080.2997914161</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>100673.708935067</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>114371.299749517</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>29.53</t>
+          <t>141163.370602808</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>119057.988207421</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.045627307212723</t>
+          <t>1066.74821994826</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.0789471581670156</t>
+          <t>1205.52451330735</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.146341531977318</t>
+          <t>1289.53611261676</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.255318926481855</t>
+          <t>1245.39953102385</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.398062215139079</t>
+          <t>1279.91735481759</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.592708488209772</t>
+          <t>1127.33890396436</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.12520113062774</t>
+          <t>1032.80722815895</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.5011408945586</t>
+          <t>920.606701366373</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.48873766149879</t>
+          <t>1007.10553278736</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.43231589474083</t>
+          <t>1063.13793825942</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.34334577326075</t>
+          <t>1041.5010841419</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1.42411600761669</t>
+          <t>1024.15691683244</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.29760586993406</t>
+          <t>1053.48608134688</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.28747681169652</t>
+          <t>1926.00239880132</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.54662060710616</t>
+          <t>1718.13968936778</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>2436941186.66372</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>2225723862.92753</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1660864887.69482</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>3172522383.32502</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3430180358.36179</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>4672046710.62388</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>2494137863.13614</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>3172417889.07175</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>6110060587.381</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>7321965120.90911</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>7515809505.80635</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>7847792384.63455</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>11092799682.3048</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>47256680852.7292</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>40345038786.3131</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>2794533021.93372</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>2666688884.92364</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1997643411.1906</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>3473223598.08151</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>3793178634.03309</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>5042301678.55913</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>2916853111.34495</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>3642846182.58457</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>6758572315.80348</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>8240214388.44689</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>8462892251.7617</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>8870029921.0651</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>12524803855.8472</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>48568798949.1502</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>41068856634.6356</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>-357591835.270002</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>-440965021.996114</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-336778523.495788</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>-300701214.756491</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-362998275.671295</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>-370254967.93525</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>-422715248.208816</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>-470428293.512824</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-648511728.422473</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>-918249267.537771</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-947082745.955353</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>-1022237536.43055</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>-1432004173.54238</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>-1312118096.42099</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>-723817848.322491</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>3893.47982849188</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.412</t>
+          <t>4015.68629094459</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>4116.55465260653</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>3936.31507285633</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>3964.21698028529</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.503</t>
+          <t>4003.51913006539</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>4111.29682553244</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>4197.64864545845</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>4331.42305363705</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>4140.71103678057</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>4285.76130727322</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>4369.10870530572</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.201</t>
+          <t>4426.09939069433</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>4459.47409392366</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>4574.35394426168</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>3194.94352599904</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>3282.04771633901</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>3394.83186660886</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>3233.74204800671</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>3260.18471284245</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>3348.5865063722</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3383.79276879293</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>3493.59664619303</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>3615.92638694828</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>3497.25987396769</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>3702.44017232506</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>3817.86499500378</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>3907.65604995853</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>3943.86870690813</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>3975.42179138642</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>443.94</t>
+          <t>28373.2571947244</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>389.57</t>
+          <t>35392.846337535</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>365.96</t>
+          <t>44182.5206399907</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>367.38</t>
+          <t>45068.0747185577</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>323.47</t>
+          <t>40944.055620681</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>42466.7268709208</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>428.76</t>
+          <t>42518.7329264322</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>510.81</t>
+          <t>42377.4179054965</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>468.48</t>
+          <t>53189.1647781823</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>426.82</t>
+          <t>71898.7903757085</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>469.69</t>
+          <t>83868.9361042611</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>486.41</t>
+          <t>96586.4794700815</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>476.39</t>
+          <t>119530.019278843</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>216.92</t>
+          <t>147548.299105145</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>256.57</t>
+          <t>117814.336000055</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>338.87</t>
+          <t>7355415079.12442</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>292.9</t>
+          <t>8981273089.5837</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>279.12</t>
+          <t>11153738457.617</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>274.2</t>
+          <t>10796792940.1916</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>257.48</t>
+          <t>10254172562.5301</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>314.77</t>
+          <t>9843278956.52852</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>359.21</t>
+          <t>12314445217.0046</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>435.85</t>
+          <t>11144111741.1508</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>401.2</t>
+          <t>11681114585.9619</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>354.26</t>
+          <t>13116331465.147</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>366.31</t>
+          <t>13379343749.7658</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>376.4</t>
+          <t>14432952121.6956</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>357.79</t>
+          <t>15442990753.3486</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>16311825167.916</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>182.05</t>
+          <t>14295689489.3812</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>151.71</t>
+          <t>36307.7524217156</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>45857.6638916735</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>115.85</t>
+          <t>52401.3801911973</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>109.42</t>
+          <t>49810.6327445414</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>45700.1926724935</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>59045.7261993691</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>169.6</t>
+          <t>44933.3115517261</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>195.69</t>
+          <t>49556.9162526708</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>173.43</t>
+          <t>66806.2088307712</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>151.03</t>
+          <t>93903.9384528349</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>158.14</t>
+          <t>112728.182904063</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>167.05</t>
+          <t>135671.407790267</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>158.39</t>
+          <t>164454.831168997</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>192754.443914157</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>136836.012423562</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>65772.47</t>
+          <t>12074138081.8645</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>69561.861</t>
+          <t>14152417803.7861</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71985.161</t>
+          <t>14966181603.2385</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70427.411</t>
+          <t>15290610730.3457</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>71880.553</t>
+          <t>15060446493.181</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>72262.497</t>
+          <t>19416494558.8422</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>72832.756</t>
+          <t>15564807877.6504</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>74602.263</t>
+          <t>16561136122.4565</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>76465.995</t>
+          <t>21823080281.5985</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>76002.452</t>
+          <t>26479301285.5032</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>81290.776</t>
+          <t>28273945151.6496</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>80528.338</t>
+          <t>31464981919.7038</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>81037.741</t>
+          <t>35907866116.8661</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>83585.565</t>
+          <t>72098156458.7316</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>84577.099</t>
+          <t>58643113430.3966</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>39680.608</t>
+          <t>-7934.49522699114</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>42135.676</t>
+          <t>-10464.8175541385</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>43213.147</t>
+          <t>-8218.85955120662</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>42440.941</t>
+          <t>-4742.55802598362</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>42560.518</t>
+          <t>-4756.13705181254</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45488.631</t>
+          <t>-16578.9993284484</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>45435.794</t>
+          <t>-2414.57862529393</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>48147.304</t>
+          <t>-7179.49834717424</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>49938.286</t>
+          <t>-13617.0440525889</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>48908.677</t>
+          <t>-22005.1480771263</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>53457.764</t>
+          <t>-28859.2467998021</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>54522.285</t>
+          <t>-39084.9283201859</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>55482.028</t>
+          <t>-44924.8118901542</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>57691.325</t>
+          <t>-45206.1448090123</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>58404.435</t>
+          <t>-19021.676423507</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>76564.093</t>
+          <t>-4718723002.74006</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>79531.698</t>
+          <t>-5171144714.20236</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>84277.044</t>
+          <t>-3812443145.62147</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>84061.256</t>
+          <t>-4493817790.15401</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>86898.315</t>
+          <t>-4806273930.65087</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>90543.161</t>
+          <t>-9573215602.31366</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>86501.423</t>
+          <t>-3250362660.64575</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>88895.18</t>
+          <t>-5417024381.30573</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>95425.408</t>
+          <t>-10141965695.6366</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>100056.014</t>
+          <t>-13362969820.3561</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>104512.503</t>
+          <t>-14894601401.8838</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>105468.203</t>
+          <t>-17032029798.0082</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>107327.017</t>
+          <t>-20464875363.5175</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>113252.337</t>
+          <t>-55786331290.8156</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>98297.92</t>
+          <t>-44347423941.0154</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>131710.48886</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>143156.42783</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>148389.08056</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>148953.04224</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>131364.75843</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>136865.93355</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>99503.9513</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>112908.61759</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>147032.50953</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>184768.03532</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>229766.68346</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.581</t>
+          <t>248927.01838</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>301232.37276</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>340491.97154</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>276089.41882</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>42290.027</t>
+          <t>0.18089520317301</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>44724.599</t>
+          <t>0.176319413809432</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45543.165</t>
+          <t>0.173604073574905</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>44236.114</t>
+          <t>0.160158023333973</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>44204.924</t>
+          <t>0.137410444688235</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>42106.389</t>
+          <t>0.144823242896442</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>42374.662</t>
+          <t>0.135239580115838</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>42318.657</t>
+          <t>0.154663284580822</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>42622.763</t>
+          <t>0.174595573165977</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>42589.201</t>
+          <t>0.174476143860154</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>44786.053</t>
+          <t>0.192828894034612</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>43941.081</t>
+          <t>0.192102753097173</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>42903.882</t>
+          <t>0.214193615790845</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>44268.897</t>
+          <t>0.184970723183781</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>43515.056</t>
+          <t>0.187392006324272</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>46762.503304833</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>55367.2707665812</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>63001.6664133908</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>64297.3387244751</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>73322.4637282348</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>73219.3651377562</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>53765.6546316908</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>53901.3390008949</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>69526.7132388374</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>89150.8864842486</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>111455.986843736</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>121229.481071189</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>149940.04512114</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>171134.668985618</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>142983.455042068</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10871.822</t>
+          <t>70161.8268922823</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>12649.293</t>
+          <t>83196.192142393</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13536.785</t>
+          <t>91495.0230014299</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13427.769</t>
+          <t>97992.2643687726</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>13741.414</t>
+          <t>106370.615282295</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12809.007</t>
+          <t>105618.88455691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>11414.018</t>
+          <t>76091.9902247633</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>10559.419</t>
+          <t>80176.3429900221</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>11611.224</t>
+          <t>102675.495454688</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>12557.425</t>
+          <t>131232.023706477</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12990.999</t>
+          <t>165554.470880223</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>12780.496</t>
+          <t>175374.24917045</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>13205.656</t>
+          <t>215287.382182296</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>24916.308</t>
+          <t>244767.100246639</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>21936.863</t>
+          <t>205621.912332655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>264.99</t>
+          <t>499474.418550874</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>233.11</t>
+          <t>533756.468206192</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>219.23</t>
+          <t>550437.999649289</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>216.07</t>
+          <t>587776.21452127</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>209.72</t>
+          <t>559877.827440956</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>255.13</t>
+          <t>582562.337127349</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>298.07</t>
+          <t>490054.966676935</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>355.97</t>
+          <t>493727.862124982</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>330.09</t>
+          <t>595800.201780415</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>289.48</t>
+          <t>745855.383845791</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>311.5</t>
+          <t>850453.953280078</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>326.61</t>
+          <t>967933.017182874</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>320.14</t>
+          <t>1128625.07103967</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>131.54</t>
+          <t>1439376.87839401</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>166.24</t>
+          <t>1175142.74268913</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5.586</t>
+          <t>70161.8268922823</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5.515</t>
+          <t>80194.8854862158</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.524</t>
+          <t>91844.8985943151</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>95943.6871792623</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.863</t>
+          <t>109779.848396017</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>116465.086951042</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>107483.918415649</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6.673</t>
+          <t>108796.177636092</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.399</t>
+          <t>111828.597308575</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4.534</t>
+          <t>124261.027676607</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3.997</t>
+          <t>142161.686312851</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>3.765</t>
+          <t>149655.75467853</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.167</t>
+          <t>158716.65869586</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2.748</t>
+          <t>164863.931029182</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t>155485.163870762</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>46762.503304833</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>54694.8969687544</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>63962.6843634089</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>66460.2088113658</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>76509.3590790499</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>82970.0897450159</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>77029.3114614993</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76759.1111493038</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>79672.9796598321</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>89362.7131902461</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>101562.088401659</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>108512.471041199</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>116135.362455626</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>121579.34525575</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>112804.144883177</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>140637.636817718</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>148188.754617607</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>152680.22428857</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>154539.676971227</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>132635.120977705</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>145202.88453309</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>113623.641135237</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>124992.106589978</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>163483.956305312</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>207633.280513523</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>253072.395029777</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>286616.30634955</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>356115.584587704</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>407405.952733361</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>339270.344477345</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>39680608026.8699</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>42135676434.5972</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>43213146757.411</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>42440940761.7936</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>42560517809.8508</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>45488630695.559</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>45435794091.9787</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>48147303842.5853</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>49938285689.8038</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>48908676733.6335</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>53457764257.9839</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>54522285202.1379</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>55482028319.7674</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>57691325215.7909</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>58404435085.5972</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>65772470036.1448</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>69561861496.2725</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>71985160813.4388</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>70427410996.0424</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>71880552548.7504</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>72262496807.5121</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>72832755555.4991</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>74602262782.8059</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>76465995304.7952</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>76002451581.0659</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>81290776423.569</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>80528338425.8053</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>81037741427.6947</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>83585565270.4043</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>84577098611.746</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>42290027358.7397</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>44724599237.9609</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>45543165415.3577</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>44236114014.8563</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>44204923535.5193</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>42106389477.5405</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>42374662069.43</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>42318657240.0706</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>42622762534.2492</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>42589201002.5229</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>44786053117.9557</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>43941080725.7726</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>42903882048.3703</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>44268897433.4793</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>43515056284.2318</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20586426.4895193</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21194652.7011088</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>21204337.5465736</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>21778920.5046377</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22048000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>21580000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>21524000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>21354000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>21147000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>21732000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>21956000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>21092505.5053513</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>20738197.1165437</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21193800.1698674</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>21275000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>10191553.5137728</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>10492770.9441879</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10497406.3031203</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10781896.2598939</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10736172.6216076</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>11362161.4429044</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>11051450.6784838</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11470065.2458555</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11529302.2804298</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>11811661.4028832</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>12473341.4731386</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>12479040.6647304</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>12535197.1165437</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12936800.1698674</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12767799.736805</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>42695615300.7843</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>44294708495.0847</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>44759106572.0011</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>43374729508.1917</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>43618102103.68</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42290062724</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>42188185937.76</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>41613735196.92</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>41088621000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>41681976000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>42517307455.04</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>41001067162.3316</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>39622583151.2949</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>40258093077.2749</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>40019217908</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>21136968495.3787</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21928843884.9571</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>22158415768.4229</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>21473141139.3276</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>21239635051.3431</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>22266289161.2901</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>21661431709.0623</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22352358238.851</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22401434330.8751</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>22654766570.73</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>24154349353.4859</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>24257620048.3281</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>23949858672.7149</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24573738602.1549</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>24016797173.8145</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.196159356914378</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.205099460499401</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.224319242464061</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.213597988326195</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.229665835837909</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.236521133701938</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.24724104079533</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.258404667943629</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.273574401952396</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.253277563370187</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.261089069051448</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.268122020559815</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.274206541122043</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.278352587450768</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.282763303894695</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.224562015410273</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.233966072771193</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.231402199416765</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.244512742989034</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.241659550790121</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.249225344328062</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.254082731610233</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.257985594241123</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.264082328164442</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.267681917957441</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.274590947512387</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.277608235050942</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.286027236388928</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.290834914191311</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.295114194482208</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.579278627675349</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.560934466729406</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.544278558119174</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.54188926868477</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.52867461337197</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.51425352197</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.498676227594436</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.483609737815248</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.462343269883162</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.479040518672372</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.464319983436165</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.454269744389243</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.439766222489029</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.430812498357921</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.422122501623098</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.272167840665116</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.28320343665693</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.305090778471066</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.290544861609576</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.312232633418881</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.317844774456991</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.330354133119758</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.343958491529621</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.360997355349063</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.335880669962547</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.350572839672933</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.362257207982644</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.370216993729715</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.376456161963932</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.382515149334895</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.283281174767894</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.29264753677969</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.287191318938563</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.303036856723649</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.296998307345724</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.304184435294129</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.308225934548862</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.309615844246565</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.31286926964477</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.321687491389864</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.321512333986268</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.31986816593863</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.325593501739573</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.328263702439916</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.330843112806146</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.44455098456699</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.42414902656338</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.407717902590371</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.406418281666775</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.390769059235395</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.377970790248881</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.36141993233138</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.346425664223814</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.326133375006167</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.342431838647589</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.327914826340799</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.317874626078726</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.304189504530712</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.295280135596152</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.286641737858959</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>382448.20652</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>412167.12829</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>444490.62229</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>456989.47529</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>456770.98809</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>503027.80797</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>393452.21779</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>437574.62436</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>568297.69543</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>720650.84726</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>888719.53974</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>979252.31131</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1200909.03839</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1358920.18054</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1114299.58345</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>210799.46371</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>231384.94676</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>244175.24729</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>252531.94134</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>239005.73626</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>250821.76909</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>189715.63136</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>205168.44958</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>266159.45176</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>338865.30422</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>418626.86591</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>461990.55552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>571402.96677</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>652173.05298</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>544892.25681</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>22789.6723488672</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>24212.6998382652</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>25938.1133696823</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>27385.3760348765</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28274.6948310621</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>29440.5458315137</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>29622.8148884805</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>30077.3742730262</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>30765.4799611517</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>32111.1917932349</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>33975.828948923</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>36018.8995046139</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>38130.594258392</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>39411.5783772959</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>40132.1943375151</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
